--- a/docs/poi/XLOOP_5km人口与到访客群估算.xlsx
+++ b/docs/poi/XLOOP_5km人口与到访客群估算.xlsx
@@ -10,19 +10,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="结论" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="街道切块" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="高校与就业" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="到访漏斗" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OSM_5km点数" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OSM_5km明细" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="大学城学生街" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="到访漏斗" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OSM_5km点数" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OSM_5km明细" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'结论'!$A$3:$D$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'街道切块'!$A$1:$G$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'高校与就业'!$A$1:$F$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'到访漏斗'!$A$1:$C$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'OSM_5km点数'!$A$1:$G$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'OSM_5km明细'!$A$1:$I$124</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'来源'!$A$1:$B$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'到访漏斗'!$A$1:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'OSM_5km点数'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'OSM_5km明细'!$A$1:$I$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'来源'!$A$1:$B$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -31,7 +32,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,6 +55,18 @@
       <name val="Microsoft YaHei"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -73,7 +86,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -95,11 +108,55 @@
         <color rgb="00D0D5DD"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D5DD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D5DD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D5DD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D5DD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D5DD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D5DD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D5DD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D5DD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -113,6 +170,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -493,9 +556,9 @@
           <t>XLOOP Park 5km 人口与到访估算（2026-08-25，圆心 34.2962N 108.7120E）</t>
         </is>
       </c>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
+      <c r="B1" s="5" t="n"/>
+      <c r="C1" s="5" t="n"/>
+      <c r="D1" s="6" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1206,6 +1269,315 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>结论：学生不能都到这条街。大学城只把商贸学院的校门口交给康定×同文；镐京、职院默认出口是吾悦。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>在校生中位</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>到本街区步行</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>到吾悦步行</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>更近的是</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>月至少来1次（街区做成）</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>大学城角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>陕西国际商贸学院</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2.0 万</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>约6分钟 / 0.47km</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>约12分钟 / 0.93km</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>本街区</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>50–70% → 1.0–1.4万</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>唯一的校门口街</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>陕西服装工程学院</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1.0 万</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>约12分钟</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>约13分钟</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>差不多</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>30–50% → 0.3–0.5万</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>争夺盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>镐京学院</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>0.79 万</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>约15分钟</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>约5分钟</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>吾悦</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>20–40%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>生活圈在吾悦口袋</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>咸阳职业技术学院</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2.0 万</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>约24分钟</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>约13分钟</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>吾悦</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>15–30%</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>出门先过吾悦</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>陕中医南校</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>0.8 万</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>约40分钟</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>约25分钟</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>吾悦</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>8–15%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>只为活动/目的地</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>五校合计</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>6.6 万</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>不是同一条街</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>约2.2–3.2万月UV</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>不是6.6万全来</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>公交证据：咸阳59路区间 咸阳大学区→商贸学院→沣西中学→吾悦→咸阳职院。统一西路才是大学城主轴。本项目在康定路南、商贸学院南侧，与沣西里抢同一条夜生活街。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>步行按4.8km/h。吾悦坐标取统一西路×白马河路约34.3028N,108.7240E；本街区圆心34.2962N,108.7120E。排序对误差不敏感。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A11:G12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1390,7 +1762,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1561,7 +1933,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1657,7 +2029,6 @@
           <t>108.709476</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>way</t>
@@ -1698,7 +2069,6 @@
           <t>108.710091</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>node</t>
@@ -1739,7 +2109,6 @@
           <t>108.715366</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>way</t>
@@ -1825,7 +2194,6 @@
           <t>108.714783</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>node</t>
@@ -1866,7 +2234,6 @@
           <t>108.712627</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>node</t>
@@ -1907,7 +2274,6 @@
           <t>108.70856</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>way</t>
@@ -1948,7 +2314,6 @@
           <t>108.712165</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>way</t>
@@ -2034,7 +2399,6 @@
           <t>108.698005</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>way</t>
@@ -2075,7 +2439,6 @@
           <t>108.726685</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>way</t>
@@ -2116,7 +2479,6 @@
           <t>108.723576</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>way</t>
@@ -2157,7 +2519,6 @@
           <t>108.710473</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>way</t>
@@ -2198,7 +2559,6 @@
           <t>108.728437</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>way</t>
@@ -2239,7 +2599,6 @@
           <t>108.719061</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>way</t>
@@ -2280,7 +2639,6 @@
           <t>108.696072</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>way</t>
@@ -2321,7 +2679,6 @@
           <t>108.691388</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>node</t>
@@ -2362,7 +2719,6 @@
           <t>108.700487</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>node</t>
@@ -2403,7 +2759,6 @@
           <t>108.691234</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>node</t>
@@ -2444,7 +2799,6 @@
           <t>108.696608</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>way</t>
@@ -2485,7 +2839,6 @@
           <t>108.733243</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>way</t>
@@ -2526,7 +2879,6 @@
           <t>108.686578</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>node</t>
@@ -2567,7 +2919,6 @@
           <t>108.732583</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>node</t>
@@ -2608,7 +2959,6 @@
           <t>108.698118</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>way</t>
@@ -2649,7 +2999,6 @@
           <t>108.723227</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>node</t>
@@ -2690,7 +3039,6 @@
           <t>108.714927</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>node</t>
@@ -2731,7 +3079,6 @@
           <t>108.727454</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>node</t>
@@ -2772,7 +3119,6 @@
           <t>108.679951</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>node</t>
@@ -2813,7 +3159,6 @@
           <t>108.729301</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>node</t>
@@ -2854,7 +3199,6 @@
           <t>108.729116</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>way</t>
@@ -2895,7 +3239,6 @@
           <t>108.728692</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>node</t>
@@ -2936,7 +3279,6 @@
           <t>108.71993</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>way</t>
@@ -2977,7 +3319,6 @@
           <t>108.709752</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>node</t>
@@ -3018,7 +3359,6 @@
           <t>108.737776</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>node</t>
@@ -3059,7 +3399,6 @@
           <t>108.683568</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>way</t>
@@ -3100,7 +3439,6 @@
           <t>108.699394</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>way</t>
@@ -3141,7 +3479,6 @@
           <t>108.724677</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>way</t>
@@ -3182,7 +3519,6 @@
           <t>108.681827</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>way</t>
@@ -3223,7 +3559,6 @@
           <t>108.682741</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>way</t>
@@ -3264,7 +3599,6 @@
           <t>108.677703</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>way</t>
@@ -3305,7 +3639,6 @@
           <t>108.6995</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>way</t>
@@ -3346,7 +3679,6 @@
           <t>108.723206</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>node</t>
@@ -3387,7 +3719,6 @@
           <t>108.672385</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>way</t>
@@ -3428,7 +3759,6 @@
           <t>108.753644</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>way</t>
@@ -3469,7 +3799,6 @@
           <t>108.68276</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>way</t>
@@ -3510,7 +3839,6 @@
           <t>108.696663</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>way</t>
@@ -3551,7 +3879,6 @@
           <t>108.67896</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>way</t>
@@ -3592,7 +3919,6 @@
           <t>108.671795</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>way</t>
@@ -3633,7 +3959,6 @@
           <t>108.679215</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>way</t>
@@ -3674,7 +3999,6 @@
           <t>108.757503</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>way</t>
@@ -3715,7 +4039,6 @@
           <t>108.713845</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>way</t>
@@ -3756,7 +4079,6 @@
           <t>108.682733</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>way</t>
@@ -3797,7 +4119,6 @@
           <t>108.711607</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>node</t>
@@ -3838,7 +4159,6 @@
           <t>108.760501</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>way</t>
@@ -3879,7 +4199,6 @@
           <t>108.726633</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>node</t>
@@ -3920,7 +4239,6 @@
           <t>108.752637</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>way</t>
@@ -3961,7 +4279,6 @@
           <t>108.751868</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>node</t>
@@ -4002,7 +4319,6 @@
           <t>108.753799</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>way</t>
@@ -4043,7 +4359,6 @@
           <t>108.679253</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>way</t>
@@ -4084,7 +4399,6 @@
           <t>108.754976</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>way</t>
@@ -4125,7 +4439,6 @@
           <t>108.700868</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>node</t>
@@ -4166,7 +4479,6 @@
           <t>108.714845</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>way</t>
@@ -4207,7 +4519,6 @@
           <t>108.709958</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>way</t>
@@ -4293,7 +4604,6 @@
           <t>108.701954</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>way</t>
@@ -4334,7 +4644,6 @@
           <t>108.698736</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>way</t>
@@ -4420,7 +4729,6 @@
           <t>108.695707</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>way</t>
@@ -4461,7 +4769,6 @@
           <t>108.692197</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>way</t>
@@ -4502,7 +4809,6 @@
           <t>108.696465</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>way</t>
@@ -4543,7 +4849,6 @@
           <t>108.695908</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>way</t>
@@ -4584,7 +4889,6 @@
           <t>108.703546</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>way</t>
@@ -4625,7 +4929,6 @@
           <t>108.70353</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>way</t>
@@ -4666,7 +4969,6 @@
           <t>108.679068</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>way</t>
@@ -4707,7 +5009,6 @@
           <t>108.678373</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>way</t>
@@ -4748,7 +5049,6 @@
           <t>108.676122</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>way</t>
@@ -4789,7 +5089,6 @@
           <t>108.67994</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>way</t>
@@ -4830,7 +5129,6 @@
           <t>108.676294</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>way</t>
@@ -4871,7 +5169,6 @@
           <t>108.74469</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>way</t>
@@ -4912,7 +5209,6 @@
           <t>108.676285</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>way</t>
@@ -4953,7 +5249,6 @@
           <t>108.697666</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>way</t>
@@ -4994,7 +5289,6 @@
           <t>108.758345</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>way</t>
@@ -5035,7 +5329,6 @@
           <t>108.677253</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>way</t>
@@ -5076,7 +5369,6 @@
           <t>108.67136</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>way</t>
@@ -5117,7 +5409,6 @@
           <t>108.672346</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>way</t>
@@ -5158,7 +5449,6 @@
           <t>108.758694</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>way</t>
@@ -5199,7 +5489,6 @@
           <t>108.677221</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>way</t>
@@ -5240,7 +5529,6 @@
           <t>108.757351</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
           <t>way</t>
@@ -5326,7 +5614,6 @@
           <t>108.692098</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
           <t>way</t>
@@ -5907,7 +6194,6 @@
           <t>108.71136</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
           <t>way</t>
@@ -6038,7 +6324,6 @@
           <t>108.693322</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
           <t>way</t>
@@ -6079,7 +6364,6 @@
           <t>108.737313</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
           <t>way</t>
@@ -6120,7 +6404,6 @@
           <t>108.682739</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
           <t>way</t>
@@ -6161,7 +6444,6 @@
           <t>108.724769</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
           <t>node</t>
@@ -6202,7 +6484,6 @@
           <t>108.702624</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
           <t>way</t>
@@ -6243,7 +6524,6 @@
           <t>108.73141</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
           <t>way</t>
@@ -6329,7 +6609,6 @@
           <t>108.702676</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
           <t>way</t>
@@ -6370,7 +6649,6 @@
           <t>108.730555</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
           <t>way</t>
@@ -6681,7 +6959,6 @@
           <t>108.702944</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
           <t>way</t>
@@ -6722,7 +6999,6 @@
           <t>108.704366</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
           <t>node</t>
@@ -6785,7 +7061,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/poi/XLOOP_5km人口与到访客群估算.xlsx
+++ b/docs/poi/XLOOP_5km人口与到访客群估算.xlsx
@@ -11,19 +11,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="街道切块" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="高校与就业" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="大学城学生街" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="到访漏斗" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OSM_5km点数" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OSM_5km明细" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="创新港与西工大" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="到访漏斗" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OSM_5km点数" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OSM_5km明细" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'结论'!$A$3:$D$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'街道切块'!$A$1:$G$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'高校与就业'!$A$1:$F$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'到访漏斗'!$A$1:$C$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'OSM_5km点数'!$A$1:$G$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'OSM_5km明细'!$A$1:$I$124</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'来源'!$A$1:$B$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'到访漏斗'!$A$1:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'OSM_5km点数'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'OSM_5km明细'!$A$1:$I$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'来源'!$A$1:$B$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1578,6 +1579,207 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>创新港：能坐1062到门口，但7km学镇当不了日常街。西工大沣西（枫溪新校区）：2027开工无学生，2030投用后才可能沿同文路北上成为第二条校门口街。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>对象</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>规模</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>到本街区</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>到吾悦</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>2027开园年</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>2030年后</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>交大创新港</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>在港学生2.1万+教授1000余</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>约7.0km；1062直达康定路同文路口；地铁5号线默认去主城</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>约8.3km（1062继续往东到白马河）</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>目的地客，月UV约0.21–0.42万；日常≈0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>仍是目的地，除非夜班公交加密</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>西工大沣西校区（枫溪/沣西新校区）</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>规划学生1.8万</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>东至同文路，OSM约2.36km正南，电动车8–12分钟</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>约3.3km，比本街区远</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>0（2027-05开工，工地无学生）</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>可能成第二基本盘，月UV约0.9–1.3万</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>西工大翱翔小镇</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>产业园/科研，不是1.8万本科宿舍</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>约4.4km</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>更远</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>周末科研人员，量级千不是万</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>与新校区联动，仍非主校门口</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>枫溪美郡</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>住宅小区，不是大学</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1.29km</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>计入5km居民，不计入师生</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>同左</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>节点：西工大2026-05交地，2027-05开工（与XLOOP开园同窗），2030-05竣工。创新港1062间隔约17分钟、末班约21点，对午夜夜场不利、对晚饭窗口有利。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A9:F10"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1762,7 +1964,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1933,7 +2135,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7061,7 +7263,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/poi/XLOOP_5km人口与到访客群估算.xlsx
+++ b/docs/poi/XLOOP_5km人口与到访客群估算.xlsx
@@ -10,21 +10,22 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="结论" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="街道切块" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="高校与就业" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="大学城学生街" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="创新港与西工大" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="到访漏斗" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OSM_5km点数" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OSM_5km明细" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名金融金科" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="大学城学生街" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="创新港与西工大" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="到访漏斗" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OSM_5km点数" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OSM_5km明细" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'结论'!$A$3:$D$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'街道切块'!$A$1:$G$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'高校与就业'!$A$1:$F$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'到访漏斗'!$A$1:$C$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'OSM_5km点数'!$A$1:$G$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'OSM_5km明细'!$A$1:$I$124</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'来源'!$A$1:$B$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'到访漏斗'!$A$1:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'OSM_5km点数'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'OSM_5km明细'!$A$1:$I$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'来源'!$A$1:$B$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -718,7 +719,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>一句话：5 公里约二十来万常住；会反复来的年轻潜客约十万；稳定年日均建议用 4000–7000 人次，不是 22 万人都会来。旁边 1.5km 沣西吾悦 2023 年客流 1600 万、商业体量约 10 倍。</t>
+          <t>一句话：5 公里约二十来万常住；会反复来的年轻潜客约十万；稳定年日均建议用 4000–7000 人次。门口点名就业：农发行金科（同文路对过，已在云谷口径，勿再加3000）+ 浙商科研（康定北，2027爬坡约0.2万，午餐更近吾悦）。旁边 1.5km 沣西吾悦 2023 年客流 1600 万、商业体量约 10 倍。</t>
         </is>
       </c>
     </row>
@@ -738,6 +739,253 @@
     <mergeCell ref="A11:D13"/>
     <mergeCell ref="A15:D15"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>条目</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>URL或出处</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>西咸七人普第二号（钓台82506/陈杨寨140286/沣西318697）</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20210923235210/http://www.xixianxinqu.gov.cn/zwgk/fdzdgknr/tjsj/60c2be5bf8fd1c0bdc315695.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>分街道转载</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://tjgb.hongheiku.com/12879.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>陈杨寨年龄结构</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hongheiku.com/xzlishi/53551.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>西咸2024常住约136.66万</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://news.qq.com/rain/a/20250831A0541100</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>商贸学院2024-09-30在校生19026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://xxgk.csiic.com/2024/0930/c4781a113161/page.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>商贸学院概况2万余/教职工1200余</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.csiic.edu.cn/3505/list.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>咸阳职院近2万</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xypi.edu.cn/about/intro.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>镐京学院本科7894（2024-12）</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>https://baike.baidu.com/item/陕西科技大学镐京学院/3958721</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>总部经济园260家/2万员工</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thepaper.cn/newsDetail_forward_14856398</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>西部云谷一期就业约4000</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thepaper.cn/newsDetail_forward_14784746</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>沣西吾悦2023销售8.18亿客流1600万</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>https://m.winshang.com/news720609.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>沣西吾悦规划约33万㎡</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>https://baike.baidu.com/item/西安沣西吾悦广场/24559073</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>橙天地用地33418㎡/建面18.3万/商业约3万</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cnr.cn/sxpd/shgl/20200730/t20200730_525187536.shtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>OSM 15km清单</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>本仓库 docs/poi/橙天地文化中心周边15km配套清单.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>农发行金融科技中心交付（云谷三期，规划五年3000）</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://sn.cri.cn/2023-09-14/dbf9dfaa-ebdf-a47f-b2ee-e3fc1dd36aae.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>农发行金科地址 康定路830号西部云谷三期</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://www.jobui.com/company/23455553/address/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>浙商银行西安科研中心揭牌（规划研发3000）</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>http://www.xixianxinqu.gov.cn:800/xwzx/xxyw/1897304443858800641.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>浙商科研中心四至：统一路南、康定路北、白马河路西；25.8万㎡</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://www.cebnet.com.cn/20241009/102971072.html</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -969,7 +1217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1241,7 +1489,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>一期约4000；多期0.5–1.0万</t>
+          <t>一期约4000；多期0.5–1.0万（含三期农发行规划3000，不是额外一层）</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -1254,7 +1502,71 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>中位0.7万</t>
+          <t>中位0.7万；农发行是点名租户</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>农发行金融科技中心（云谷三期）</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>过同文路约5–8分钟</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2023-09-12交付；地上8.23万㎡；规划五年3000中高级人才；在岗未公开</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>已含在云谷0.7万内；2027爬坡约0.15–0.25万在场</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>点名即可，禁止再加3000</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>cri.cn 2023-09-14；职友集 康定路830号西部云谷三期</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>浙商银行科研中心（西安）</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>沿康定东约1.0–1.3km；距吾悦约280m</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>25亿/25.8万㎡；2025-02-28揭牌；规划研发约3000</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>约2000（2027爬坡；规划3000后期）</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>独立园区；2027爬坡约0.15–0.25万，午餐默认可去吾悦</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>xixianxinqu.gov.cn 揭牌稿；cebnet 四至：统一路南、康定路北、白马河路西</t>
         </is>
       </c>
     </row>
@@ -1265,6 +1577,198 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>口语</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>到本街区</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>到吾悦</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>公开规模</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>2027怎么用</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>中国农业发展银行金融科技中心</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>农发行金科中心</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>西部云谷三期，康定路830号；康定路以南、同文路以东/学林路以西</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>过同文路步行约5–8分钟</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>约1.5km级，比本街区远</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2023-09-12交付；地上约8.23万㎡，5栋办公+人才公寓；规划五年3000</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>已在云谷0.7万口径；2027爬坡0.15–0.25万在场；点名不另加</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://sn.cri.cn/2023-09-14/dbf9dfaa-ebdf-a47f-b2ee-e3fc1dd36aae.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>浙商银行科研中心（西安）</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>浙商科研</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>统一路以南、康定路以北、白马河路以西（康定×白马河西北角）</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>沿康定路往东约1.0–1.3km</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>约280m（商场默认午餐）</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>总投资25亿，建面25.8万㎡；2025-02-28揭牌；规划研发约3000</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>独立园区；2027爬坡0.15–0.25万；不要写成3000人天天来南门吃饭</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>http://www.xixianxinqu.gov.cn:800/xwzx/xxyw/1897304443858800641.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>金科·世界城（不要混）</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>住宅，不是农发行金科</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>OSM 住宅 1.24km</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>OSM way 1019719817</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>禁止和农发行金科中心混名</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>docs/poi/橙天地文化中心周边15km配套清单.csv</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1573,7 +2077,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1774,7 +2278,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1859,17 +2363,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>D 总部经济园+云谷白领</t>
+          <t>D 总部+云谷（含农发行）+浙商爬坡</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>约 2.7 万</t>
+          <t>约 2.9 万</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>与B、C重叠</t>
+          <t>与B、C重叠；农发行不另加，浙商2027约0.2万</t>
         </is>
       </c>
     </row>
@@ -1964,7 +2468,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2135,7 +2639,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7261,203 +7765,4 @@
   <autoFilter ref="A1:I124"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>条目</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>URL或出处</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>西咸七人普第二号（钓台82506/陈杨寨140286/沣西318697）</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20210923235210/http://www.xixianxinqu.gov.cn/zwgk/fdzdgknr/tjsj/60c2be5bf8fd1c0bdc315695.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>分街道转载</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>https://tjgb.hongheiku.com/12879.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>陈杨寨年龄结构</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.hongheiku.com/xzlishi/53551.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>西咸2024常住约136.66万</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>https://news.qq.com/rain/a/20250831A0541100</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>商贸学院2024-09-30在校生19026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>https://xxgk.csiic.com/2024/0930/c4781a113161/page.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>商贸学院概况2万余/教职工1200余</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.csiic.edu.cn/3505/list.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>咸阳职院近2万</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xypi.edu.cn/about/intro.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>镐京学院本科7894（2024-12）</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>https://baike.baidu.com/item/陕西科技大学镐京学院/3958721</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>总部经济园260家/2万员工</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.thepaper.cn/newsDetail_forward_14856398</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>西部云谷一期就业约4000</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.thepaper.cn/newsDetail_forward_14784746</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>沣西吾悦2023销售8.18亿客流1600万</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>https://m.winshang.com/news720609.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>沣西吾悦规划约33万㎡</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>https://baike.baidu.com/item/西安沣西吾悦广场/24559073</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>橙天地用地33418㎡/建面18.3万/商业约3万</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>http://www.cnr.cn/sxpd/shgl/20200730/t20200730_525187536.shtml</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>OSM 15km清单</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>本仓库 docs/poi/橙天地文化中心周边15km配套清单.csv</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:B15"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>